--- a/Data/HellLevel.xlsx
+++ b/Data/HellLevel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9995C65-B63D-4476-A66C-915C312FA831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30016DAB-0B55-4835-B66B-9360850E1994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19350" yWindow="0" windowWidth="19155" windowHeight="10545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13950" yWindow="2565" windowWidth="25350" windowHeight="10530" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HellLevel" sheetId="1" r:id="rId1"/>
@@ -33,13 +33,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Exp</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>HellLevel</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LevelUpTimeSec</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -495,7 +499,7 @@
   <sheetPr codeName="Sheet4">
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:B1221"/>
+  <dimension ref="A1:C1221"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5" style="3" bestFit="1" customWidth="1"/>
@@ -505,147 +509,201 @@
     <col min="105" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="150" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="150" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C1" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6">
         <v>1</v>
       </c>
       <c r="B2" s="6">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C2" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6">
         <v>2</v>
       </c>
       <c r="B3" s="6">
         <v>250</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6">
         <v>3</v>
       </c>
       <c r="B4" s="6">
         <v>500</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C4" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6">
         <v>4</v>
       </c>
       <c r="B5" s="6">
         <v>800</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C5" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6">
         <v>5</v>
       </c>
       <c r="B6" s="6">
         <v>1300</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C6" s="1">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6">
         <v>6</v>
       </c>
       <c r="B7" s="6">
         <v>1800</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C7" s="1">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6">
         <v>7</v>
       </c>
       <c r="B8" s="6">
         <v>2400</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C8" s="1">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6">
         <v>8</v>
       </c>
       <c r="B9" s="6">
         <v>3200</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C9" s="1">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6">
         <v>9</v>
       </c>
       <c r="B10" s="6">
         <v>4100</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C10" s="1">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6">
         <v>10</v>
       </c>
       <c r="B11" s="6">
         <v>5400</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C11" s="1">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="6">
         <v>11</v>
       </c>
       <c r="B12" s="6">
         <v>7000</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C12" s="1">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6">
         <v>12</v>
       </c>
       <c r="B13" s="6">
         <v>9300</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C13" s="1">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="6">
         <v>13</v>
       </c>
       <c r="B14" s="6">
         <v>12100</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C14" s="1">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="6">
         <v>14</v>
       </c>
       <c r="B15" s="6">
         <v>15600</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C15" s="1">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="6">
         <v>15</v>
       </c>
       <c r="B16" s="6">
         <v>31200</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C16" s="1">
+        <v>3120</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="6">
         <v>16</v>
       </c>
       <c r="B17" s="6">
         <v>46800</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C17" s="1">
+        <v>4680</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="6">
         <v>17</v>
       </c>
       <c r="B18" s="6">
+        <v>-1</v>
+      </c>
+      <c r="C18" s="1">
         <v>-1</v>
       </c>
     </row>

--- a/Data/HellLevel.xlsx
+++ b/Data/HellLevel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30016DAB-0B55-4835-B66B-9360850E1994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B72A7EA7-F61A-47B4-917C-A668608A4D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13950" yWindow="2565" windowWidth="25350" windowHeight="10530" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5805" yWindow="1785" windowWidth="25350" windowHeight="10530" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HellLevel" sheetId="1" r:id="rId1"/>
@@ -525,7 +525,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="6">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1">
         <v>10</v>
@@ -536,7 +536,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="6">
-        <v>250</v>
+        <v>25</v>
       </c>
       <c r="C3" s="1">
         <v>25</v>
@@ -547,7 +547,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="C4" s="1">
         <v>50</v>
@@ -558,7 +558,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>800</v>
+        <v>80</v>
       </c>
       <c r="C5" s="1">
         <v>80</v>
@@ -569,7 +569,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6">
-        <v>1300</v>
+        <v>130</v>
       </c>
       <c r="C6" s="1">
         <v>130</v>
@@ -580,7 +580,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6">
-        <v>1800</v>
+        <v>180</v>
       </c>
       <c r="C7" s="1">
         <v>180</v>
@@ -591,7 +591,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="6">
-        <v>2400</v>
+        <v>240</v>
       </c>
       <c r="C8" s="1">
         <v>240</v>
@@ -602,7 +602,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6">
-        <v>3200</v>
+        <v>320</v>
       </c>
       <c r="C9" s="1">
         <v>320</v>
@@ -613,7 +613,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="6">
-        <v>4100</v>
+        <v>410</v>
       </c>
       <c r="C10" s="1">
         <v>410</v>
@@ -624,7 +624,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="6">
-        <v>5400</v>
+        <v>540</v>
       </c>
       <c r="C11" s="1">
         <v>540</v>
@@ -635,7 +635,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="6">
-        <v>7000</v>
+        <v>700</v>
       </c>
       <c r="C12" s="1">
         <v>700</v>
@@ -646,7 +646,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="6">
-        <v>9300</v>
+        <v>930</v>
       </c>
       <c r="C13" s="1">
         <v>930</v>
@@ -657,7 +657,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="6">
-        <v>12100</v>
+        <v>1210</v>
       </c>
       <c r="C14" s="1">
         <v>1210</v>
@@ -668,7 +668,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="6">
-        <v>15600</v>
+        <v>1560</v>
       </c>
       <c r="C15" s="1">
         <v>1560</v>
@@ -679,7 +679,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="6">
-        <v>31200</v>
+        <v>3120</v>
       </c>
       <c r="C16" s="1">
         <v>3120</v>
@@ -690,7 +690,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="6">
-        <v>46800</v>
+        <v>4680</v>
       </c>
       <c r="C17" s="1">
         <v>4680</v>

--- a/Data/HellLevel.xlsx
+++ b/Data/HellLevel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B72A7EA7-F61A-47B4-917C-A668608A4D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D314EC30-C944-4B37-A979-1599AEF93778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5805" yWindow="1785" windowWidth="25350" windowHeight="10530" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -525,10 +525,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -536,10 +536,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="6">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -547,10 +547,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="6">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="C4" s="1">
-        <v>50</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -558,10 +558,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C5" s="1">
-        <v>80</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -569,10 +569,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="6">
-        <v>130</v>
+        <v>1</v>
       </c>
       <c r="C6" s="1">
-        <v>130</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -580,10 +580,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="6">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="C7" s="1">
-        <v>180</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -591,10 +591,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="6">
-        <v>240</v>
+        <v>1</v>
       </c>
       <c r="C8" s="1">
-        <v>240</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -602,10 +602,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="6">
-        <v>320</v>
+        <v>1</v>
       </c>
       <c r="C9" s="1">
-        <v>320</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -613,10 +613,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="6">
-        <v>410</v>
+        <v>1</v>
       </c>
       <c r="C10" s="1">
-        <v>410</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -624,10 +624,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="6">
-        <v>540</v>
+        <v>1</v>
       </c>
       <c r="C11" s="1">
-        <v>540</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -635,10 +635,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="6">
-        <v>700</v>
+        <v>1</v>
       </c>
       <c r="C12" s="1">
-        <v>700</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -646,10 +646,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="6">
-        <v>930</v>
+        <v>1</v>
       </c>
       <c r="C13" s="1">
-        <v>930</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -657,10 +657,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="6">
-        <v>1210</v>
+        <v>1</v>
       </c>
       <c r="C14" s="1">
-        <v>1210</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -668,10 +668,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="6">
-        <v>1560</v>
+        <v>1</v>
       </c>
       <c r="C15" s="1">
-        <v>1560</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -679,10 +679,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="6">
-        <v>3120</v>
+        <v>1</v>
       </c>
       <c r="C16" s="1">
-        <v>3120</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -690,10 +690,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="6">
-        <v>4680</v>
+        <v>1</v>
       </c>
       <c r="C17" s="1">
-        <v>4680</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
